--- a/data/visitors_sample_10.xlsx
+++ b/data/visitors_sample_10.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="visitors" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,23 +27,17 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,14 +45,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -134,58 +134,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>Must match the visitor user account username.</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>Use 'visitor'.</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>Business-facing code, e.g. VIS-001.</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>Default daily visit capacity.</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>TRUE/FALSE</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Visitors10Template" displayName="Visitors10Template" ref="A1:H11" headerRowCount="1">
-  <autoFilter ref="A1:H11"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="username"/>
-    <tableColumn id="2" name="role"/>
-    <tableColumn id="3" name="visitor_code"/>
-    <tableColumn id="4" name="full_name"/>
-    <tableColumn id="5" name="default_start_lat"/>
-    <tableColumn id="6" name="default_start_lon"/>
-    <tableColumn id="7" name="default_capacity"/>
-    <tableColumn id="8" name="is_active"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -479,16 +427,6 @@
   </sheetPr>
   <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -550,14 +488,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Visitor 1</t>
+          <t>ویزیتور 01</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>35.779618</v>
+        <v>35.67</v>
       </c>
       <c r="F2" t="n">
-        <v>51.403305</v>
+        <v>51.33</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -584,14 +522,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Visitor 2</t>
+          <t>ویزیتور 02</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>35.742861</v>
+        <v>35.68</v>
       </c>
       <c r="F3" t="n">
-        <v>51.365318</v>
+        <v>51.34</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -618,14 +556,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Visitor 3</t>
+          <t>ویزیتور 03</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>35.713121</v>
+        <v>35.69</v>
       </c>
       <c r="F4" t="n">
-        <v>51.546172</v>
+        <v>51.35</v>
       </c>
       <c r="G4" t="n">
         <v>30</v>
@@ -652,14 +590,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Visitor 4</t>
+          <t>ویزیتور 04</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>35.745966</v>
+        <v>35.7</v>
       </c>
       <c r="F5" t="n">
-        <v>51.244363</v>
+        <v>51.36</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -686,14 +624,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Visitor 5</t>
+          <t>ویزیتور 05</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>35.660694</v>
+        <v>35.71</v>
       </c>
       <c r="F6" t="n">
-        <v>51.387886</v>
+        <v>51.37</v>
       </c>
       <c r="G6" t="n">
         <v>30</v>
@@ -720,14 +658,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Visitor 6</t>
+          <t>ویزیتور 06</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>35.782983</v>
+        <v>35.72</v>
       </c>
       <c r="F7" t="n">
-        <v>51.427643</v>
+        <v>51.38</v>
       </c>
       <c r="G7" t="n">
         <v>30</v>
@@ -754,14 +692,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Visitor 7</t>
+          <t>ویزیتور 07</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>35.716047</v>
+        <v>35.73</v>
       </c>
       <c r="F8" t="n">
-        <v>51.334606</v>
+        <v>51.39</v>
       </c>
       <c r="G8" t="n">
         <v>30</v>
@@ -788,14 +726,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Visitor 8</t>
+          <t>ویزیتور 08</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>35.737679</v>
+        <v>35.74</v>
       </c>
       <c r="F9" t="n">
-        <v>51.466061</v>
+        <v>51.4</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -822,14 +760,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Visitor 9</t>
+          <t>ویزیتور 09</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>35.715565</v>
+        <v>35.75</v>
       </c>
       <c r="F10" t="n">
-        <v>51.271759</v>
+        <v>51.41</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -856,14 +794,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Visitor 10</t>
+          <t>ویزیتور 10</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>35.658157</v>
+        <v>35.76</v>
       </c>
       <c r="F11" t="n">
-        <v>51.358548</v>
+        <v>51.42</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -874,9 +812,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>